--- a/cet4/result/21_职场逆袭_女秘书的总裁之路/21_职场逆袭_女秘书的总裁之路_学习版.xlsx
+++ b/cet4/result/21_职场逆袭_女秘书的总裁之路/21_职场逆袭_女秘书的总裁之路_学习版.xlsx
@@ -397,983 +397,689 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D48"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>depart</v>
       </c>
       <c r="B2" t="str">
-        <v>depart</v>
+        <v>/dɪˈpɑːrt/</v>
       </c>
       <c r="C2" t="str">
+        <v>vi./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>离开</v>
       </c>
-      <c r="D2" t="str">
-        <v>depart(离开)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>chocolate</v>
       </c>
       <c r="B3" t="str">
-        <v>chocolate</v>
+        <v>/ˈtʃɔːklət/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>巧克力</v>
       </c>
-      <c r="D3" t="str">
-        <v>chocolate(巧克力)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>mountain</v>
       </c>
       <c r="B4" t="str">
-        <v>mountain</v>
+        <v>/ˈmaʊntn/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>山</v>
       </c>
-      <c r="D4" t="str">
-        <v>mountain(山)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>van</v>
       </c>
       <c r="B5" t="str">
-        <v>van</v>
+        <v>/væn/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D5" t="str">
         <v>厢式货车</v>
       </c>
-      <c r="D5" t="str">
-        <v>van(厢式货车)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>apartment</v>
       </c>
       <c r="B6" t="str">
-        <v>apartment</v>
+        <v>/əˈpɑːrtmənt/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>公寓</v>
       </c>
-      <c r="D6" t="str">
-        <v>apartment(公寓)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>clean</v>
       </c>
       <c r="B7" t="str">
-        <v>apartment</v>
+        <v>/kliːn/</v>
       </c>
       <c r="C7" t="str">
-        <v>公寓</v>
+        <v>n./vt./vi./v./adj./adv.</v>
       </c>
       <c r="D7" t="str">
-        <v>apartment(公寓)📢</v>
+        <v>干净的</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>container</v>
       </c>
       <c r="B8" t="str">
-        <v>clean</v>
+        <v>/kənˈteɪnər/</v>
       </c>
       <c r="C8" t="str">
-        <v>干净的</v>
+        <v>n.</v>
       </c>
       <c r="D8" t="str">
-        <v>clean(干净的)📢</v>
+        <v>容器</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>movie</v>
       </c>
       <c r="B9" t="str">
-        <v>container</v>
+        <v>/ˈmuːvi/</v>
       </c>
       <c r="C9" t="str">
-        <v>容器</v>
+        <v>n./adj.</v>
       </c>
       <c r="D9" t="str">
-        <v>container(容器)📢</v>
+        <v>电影</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>advertisement</v>
       </c>
       <c r="B10" t="str">
-        <v>movie</v>
+        <v>/ˌædvərˈtaɪzmənt/</v>
       </c>
       <c r="C10" t="str">
-        <v>电影</v>
+        <v>n.</v>
       </c>
       <c r="D10" t="str">
-        <v>movie(电影)📢</v>
+        <v>广告</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>blackboard</v>
       </c>
       <c r="B11" t="str">
-        <v>advertisement</v>
+        <v>/ˈblækbɔːrd/</v>
       </c>
       <c r="C11" t="str">
-        <v>广告</v>
+        <v>n.</v>
       </c>
       <c r="D11" t="str">
-        <v>advertisement(广告)📢</v>
+        <v>黑板</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>engineer</v>
       </c>
       <c r="B12" t="str">
-        <v>blackboard</v>
+        <v>/ˌendʒɪˈnɪr/</v>
       </c>
       <c r="C12" t="str">
-        <v>黑板</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D12" t="str">
-        <v>blackboard(黑板)📢</v>
+        <v>工程师</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>everyday</v>
       </c>
       <c r="B13" t="str">
-        <v>engineer</v>
+        <v>/ˈevrideɪ/</v>
       </c>
       <c r="C13" t="str">
-        <v>工程师</v>
+        <v>n./adj.</v>
       </c>
       <c r="D13" t="str">
-        <v>engineer(工程师)📢</v>
+        <v>每天的</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>progressive</v>
       </c>
       <c r="B14" t="str">
-        <v>everyday</v>
+        <v>/prəˈɡresɪv/</v>
       </c>
       <c r="C14" t="str">
-        <v>每天的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D14" t="str">
-        <v>everyday(每天的)📢</v>
+        <v>进步的</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>emphasis</v>
       </c>
       <c r="B15" t="str">
-        <v>progressive</v>
+        <v>/ˈemfəsɪs/</v>
       </c>
       <c r="C15" t="str">
-        <v>进步的</v>
+        <v>n.</v>
       </c>
       <c r="D15" t="str">
-        <v>progressive(进步的)📢</v>
+        <v>重点</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>hotel</v>
       </c>
       <c r="B16" t="str">
-        <v>emphasis</v>
+        <v>/hoʊˈtel/</v>
       </c>
       <c r="C16" t="str">
-        <v>重点</v>
+        <v>n.</v>
       </c>
       <c r="D16" t="str">
-        <v>emphasis(重点)📢</v>
+        <v>旅馆</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>porridge</v>
       </c>
       <c r="B17" t="str">
-        <v>hotel</v>
+        <v>/ˈpɔːrɪdʒ/</v>
       </c>
       <c r="C17" t="str">
-        <v>旅馆</v>
+        <v>n./vt.</v>
       </c>
       <c r="D17" t="str">
-        <v>hotel(旅馆)📢</v>
+        <v>粥</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>prove</v>
       </c>
       <c r="B18" t="str">
-        <v>porridge</v>
+        <v>/pruːv/</v>
       </c>
       <c r="C18" t="str">
-        <v>粥</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D18" t="str">
-        <v>porridge(粥)📢</v>
+        <v>证明</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>total</v>
       </c>
       <c r="B19" t="str">
-        <v>prove</v>
+        <v>/ˈtoʊtl/</v>
       </c>
       <c r="C19" t="str">
-        <v>证明</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D19" t="str">
-        <v>prove(证明)📢</v>
+        <v>全部的</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>election</v>
       </c>
       <c r="B20" t="str">
-        <v>total</v>
+        <v>/ɪˈlekʃn/</v>
       </c>
       <c r="C20" t="str">
-        <v>全部的</v>
+        <v>n.</v>
       </c>
       <c r="D20" t="str">
-        <v>total(全部的)📢</v>
+        <v>选举</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>article</v>
       </c>
       <c r="B21" t="str">
-        <v>election</v>
+        <v>/ˈɑːrtɪkl/</v>
       </c>
       <c r="C21" t="str">
-        <v>选举</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D21" t="str">
-        <v>election(选举)📢</v>
+        <v>文章</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>own</v>
       </c>
       <c r="B22" t="str">
-        <v>article</v>
+        <v>/oʊn/</v>
       </c>
       <c r="C22" t="str">
-        <v>文章</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D22" t="str">
-        <v>article(文章)📢</v>
+        <v>自己的</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>grocer</v>
       </c>
       <c r="B23" t="str">
-        <v>own</v>
+        <v>/ˈɡroʊsər/</v>
       </c>
       <c r="C23" t="str">
-        <v>自己的</v>
+        <v>n.</v>
       </c>
       <c r="D23" t="str">
-        <v>own(自己的)📢</v>
+        <v>杂货店</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>banana</v>
       </c>
       <c r="B24" t="str">
-        <v>grocer</v>
+        <v>/bəˈnænə/</v>
       </c>
       <c r="C24" t="str">
-        <v>杂货店</v>
+        <v>n.</v>
       </c>
       <c r="D24" t="str">
-        <v>grocer(杂货店)📢</v>
+        <v>香蕉</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>situation</v>
       </c>
       <c r="B25" t="str">
-        <v>banana</v>
+        <v>/ˌsɪtʃuˈeɪʃn/</v>
       </c>
       <c r="C25" t="str">
-        <v>香蕉</v>
+        <v>n.</v>
       </c>
       <c r="D25" t="str">
-        <v>banana(香蕉)📢</v>
+        <v>情况</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>strange</v>
       </c>
       <c r="B26" t="str">
-        <v>situation</v>
+        <v>/streɪndʒ/</v>
       </c>
       <c r="C26" t="str">
-        <v>情况</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D26" t="str">
-        <v>situation(情况)📢</v>
+        <v>奇怪的</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>disk</v>
       </c>
       <c r="B27" t="str">
-        <v>strange</v>
+        <v>/dɪsk/</v>
       </c>
       <c r="C27" t="str">
-        <v>奇怪的</v>
+        <v>n.</v>
       </c>
       <c r="D27" t="str">
-        <v>strange(奇怪的)📢</v>
+        <v>磁盘</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>scholar</v>
       </c>
       <c r="B28" t="str">
-        <v>disk</v>
+        <v>/ˈskɑːlər/</v>
       </c>
       <c r="C28" t="str">
-        <v>磁盘</v>
+        <v>n.</v>
       </c>
       <c r="D28" t="str">
-        <v>disk(磁盘)📢</v>
+        <v>学者</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>occasionally</v>
       </c>
       <c r="B29" t="str">
-        <v>hotel</v>
+        <v>/əˈkeɪʒnəli/</v>
       </c>
       <c r="C29" t="str">
-        <v>旅馆</v>
+        <v>v./adv.</v>
       </c>
       <c r="D29" t="str">
-        <v>hotel(旅馆)📢</v>
+        <v>偶尔</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>Marxist</v>
       </c>
       <c r="B30" t="str">
-        <v>emphasis</v>
+        <v>/ˈmɑːrksɪst/</v>
       </c>
       <c r="C30" t="str">
-        <v>强调</v>
+        <v>n./adj.</v>
       </c>
       <c r="D30" t="str">
-        <v>emphasis(强调)📢</v>
+        <v>马克思主义者</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>honour</v>
       </c>
       <c r="B31" t="str">
-        <v>scholar</v>
+        <v>/ˈɑːnər/</v>
       </c>
       <c r="C31" t="str">
-        <v>学者</v>
+        <v>n./vt.</v>
       </c>
       <c r="D31" t="str">
-        <v>scholar(学者)📢</v>
+        <v>荣誉</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>mass</v>
       </c>
       <c r="B32" t="str">
-        <v>occasionally</v>
+        <v>/mæs/</v>
       </c>
       <c r="C32" t="str">
-        <v>偶尔</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D32" t="str">
-        <v>occasionally(偶尔)📢</v>
+        <v>群众</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>radio</v>
       </c>
       <c r="B33" t="str">
-        <v>Marxist</v>
+        <v>/ˈreɪdioʊ/</v>
       </c>
       <c r="C33" t="str">
-        <v>马克思主义者</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>Marxist(马克思主义者)📢</v>
+        <v>收音机</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>nurse</v>
       </c>
       <c r="B34" t="str">
-        <v>prove</v>
+        <v>/nɜːrs/</v>
       </c>
       <c r="C34" t="str">
-        <v>证明</v>
+        <v>n./vt./v.</v>
       </c>
       <c r="D34" t="str">
-        <v>prove(证明)📢</v>
+        <v>护士</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>violent</v>
       </c>
       <c r="B35" t="str">
-        <v>honour</v>
+        <v>/ˈvaɪələnt/</v>
       </c>
       <c r="C35" t="str">
-        <v>荣誉</v>
+        <v>adj.</v>
       </c>
       <c r="D35" t="str">
-        <v>honour(荣誉)📢</v>
+        <v>猛烈的</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>bloom</v>
       </c>
       <c r="B36" t="str">
-        <v>mass</v>
+        <v>/bluːm/</v>
       </c>
       <c r="C36" t="str">
-        <v>群众</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>mass(群众)📢</v>
+        <v>开花</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>foreigner</v>
       </c>
       <c r="B37" t="str">
-        <v>radio</v>
+        <v>/ˈfɔːrənər/</v>
       </c>
       <c r="C37" t="str">
-        <v>收音机</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>radio(收音机)📢</v>
+        <v>外国人</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>lest</v>
       </c>
       <c r="B38" t="str">
-        <v>mountain</v>
+        <v>/lest/</v>
       </c>
       <c r="C38" t="str">
-        <v>山</v>
+        <v>conj.</v>
       </c>
       <c r="D38" t="str">
-        <v>mountain(山)📢</v>
+        <v>以免</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>myself</v>
       </c>
       <c r="B39" t="str">
-        <v>nurse</v>
+        <v>/maɪˈself/</v>
       </c>
       <c r="C39" t="str">
-        <v>护士</v>
+        <v>n./pron.</v>
       </c>
       <c r="D39" t="str">
-        <v>nurse(护士)📢</v>
+        <v>我自己</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>plain</v>
       </c>
       <c r="B40" t="str">
-        <v>everyday</v>
+        <v>/pleɪn/</v>
       </c>
       <c r="C40" t="str">
-        <v>日常的</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D40" t="str">
-        <v>everyday(日常的)📢</v>
+        <v>简单的</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>reinforce</v>
       </c>
       <c r="B41" t="str">
-        <v>violent</v>
+        <v>/ˌriːɪnˈfɔːrs/</v>
       </c>
       <c r="C41" t="str">
-        <v>猛烈的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D41" t="str">
-        <v>violent(猛烈的)📢</v>
+        <v>加强</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>failure</v>
       </c>
       <c r="B42" t="str">
-        <v>bloom</v>
+        <v>/ˈfeɪljər/</v>
       </c>
       <c r="C42" t="str">
-        <v>开花</v>
+        <v>n.</v>
       </c>
       <c r="D42" t="str">
-        <v>bloom(开花)📢</v>
+        <v>失败</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>missile</v>
       </c>
       <c r="B43" t="str">
-        <v>movie</v>
+        <v>/ˈmɪsl/</v>
       </c>
       <c r="C43" t="str">
-        <v>电影</v>
+        <v>n./adj.</v>
       </c>
       <c r="D43" t="str">
-        <v>movie(电影)📢</v>
+        <v>导弹</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>rifle</v>
       </c>
       <c r="B44" t="str">
-        <v>chocolate</v>
+        <v>/ˈraɪfl/</v>
       </c>
       <c r="C44" t="str">
-        <v>巧克力</v>
+        <v>n./vt.</v>
       </c>
       <c r="D44" t="str">
-        <v>chocolate(巧克力)📢</v>
+        <v>步枪</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>shell</v>
       </c>
       <c r="B45" t="str">
-        <v>foreigner</v>
+        <v>/ʃel/</v>
       </c>
       <c r="C45" t="str">
-        <v>外国人</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>foreigner(外国人)📢</v>
+        <v>炮弹</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>tin</v>
       </c>
       <c r="B46" t="str">
-        <v>lest</v>
+        <v>/tɪn/</v>
       </c>
       <c r="C46" t="str">
-        <v>以免</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D46" t="str">
-        <v>lest(以免)📢</v>
+        <v>锡</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>elimination</v>
       </c>
       <c r="B47" t="str">
-        <v>foreigner</v>
+        <v>/ɪˌlɪmɪˈneɪʃn/</v>
       </c>
       <c r="C47" t="str">
-        <v>外国人</v>
+        <v>n.</v>
       </c>
       <c r="D47" t="str">
-        <v>foreigner(外国人)📢</v>
+        <v>消除</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>oblige</v>
       </c>
       <c r="B48" t="str">
-        <v>foreigner</v>
+        <v>/əˈblaɪdʒ/</v>
       </c>
       <c r="C48" t="str">
-        <v>外国人</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D48" t="str">
-        <v>foreigner(外国人)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>foreigner</v>
-      </c>
-      <c r="C49" t="str">
-        <v>外国人</v>
-      </c>
-      <c r="D49" t="str">
-        <v>foreigner(外国人)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>myself</v>
-      </c>
-      <c r="C50" t="str">
-        <v>我自己</v>
-      </c>
-      <c r="D50" t="str">
-        <v>myself(我自己)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>plain</v>
-      </c>
-      <c r="C51" t="str">
-        <v>简单的</v>
-      </c>
-      <c r="D51" t="str">
-        <v>plain(简单的)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>reinforce</v>
-      </c>
-      <c r="C52" t="str">
-        <v>加强</v>
-      </c>
-      <c r="D52" t="str">
-        <v>reinforce(加强)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>failure</v>
-      </c>
-      <c r="C53" t="str">
-        <v>失败</v>
-      </c>
-      <c r="D53" t="str">
-        <v>failure(失败)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>missile</v>
-      </c>
-      <c r="C54" t="str">
-        <v>导弹</v>
-      </c>
-      <c r="D54" t="str">
-        <v>missile(导弹)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>rifle</v>
-      </c>
-      <c r="C55" t="str">
-        <v>步枪</v>
-      </c>
-      <c r="D55" t="str">
-        <v>rifle(步枪)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>shell</v>
-      </c>
-      <c r="C56" t="str">
-        <v>炮弹</v>
-      </c>
-      <c r="D56" t="str">
-        <v>shell(炮弹)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>bloom</v>
-      </c>
-      <c r="C57" t="str">
-        <v>开花</v>
-      </c>
-      <c r="D57" t="str">
-        <v>bloom(开花)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>porridge</v>
-      </c>
-      <c r="C58" t="str">
-        <v>粥</v>
-      </c>
-      <c r="D58" t="str">
-        <v>porridge(粥)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>myself</v>
-      </c>
-      <c r="C59" t="str">
-        <v>我自己</v>
-      </c>
-      <c r="D59" t="str">
-        <v>myself(我自己)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>depart</v>
-      </c>
-      <c r="C60" t="str">
-        <v>离开</v>
-      </c>
-      <c r="D60" t="str">
-        <v>depart(离开)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>chocolate</v>
-      </c>
-      <c r="C61" t="str">
-        <v>巧克力</v>
-      </c>
-      <c r="D61" t="str">
-        <v>chocolate(巧克力)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>tin</v>
-      </c>
-      <c r="C62" t="str">
-        <v>锡</v>
-      </c>
-      <c r="D62" t="str">
-        <v>tin(锡)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>tin</v>
-      </c>
-      <c r="C63" t="str">
-        <v>锡</v>
-      </c>
-      <c r="D63" t="str">
-        <v>tin(锡)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>elimination</v>
-      </c>
-      <c r="C64" t="str">
-        <v>消除</v>
-      </c>
-      <c r="D64" t="str">
-        <v>elimination(消除)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>oblige</v>
-      </c>
-      <c r="C65" t="str">
         <v>迫使</v>
-      </c>
-      <c r="D65" t="str">
-        <v>oblige(迫使)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>lest</v>
-      </c>
-      <c r="C66" t="str">
-        <v>以免</v>
-      </c>
-      <c r="D66" t="str">
-        <v>lest(以免)📢</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>honour</v>
-      </c>
-      <c r="C67" t="str">
-        <v>荣誉</v>
-      </c>
-      <c r="D67" t="str">
-        <v>honour(荣誉)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>plain</v>
-      </c>
-      <c r="C68" t="str">
-        <v>朴素的</v>
-      </c>
-      <c r="D68" t="str">
-        <v>plain(朴素的)📢</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
-        <v>bloom</v>
-      </c>
-      <c r="C69" t="str">
-        <v>开花</v>
-      </c>
-      <c r="D69" t="str">
-        <v>bloom(开花)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D48"/>
   </ignoredErrors>
 </worksheet>
 </file>